--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>Week</t>
   </si>
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +225,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -535,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
@@ -602,7 +605,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="1">
-        <v>92.07</v>
+        <v>92.57</v>
       </c>
       <c r="F2">
         <f>ROUND(AVERAGE(H2:N2), 2)</f>
@@ -647,7 +650,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="1">
-        <v>91.15</v>
+        <v>91.64</v>
       </c>
       <c r="F3">
         <f>ROUND(AVERAGE(H3:N3), 2)</f>
@@ -692,7 +695,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="1">
-        <v>90.24</v>
+        <v>90.72</v>
       </c>
       <c r="F4">
         <f>ROUND(AVERAGE(H4:N4), 2)</f>
@@ -736,8 +739,8 @@
       <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1">
-        <v>89.34</v>
+      <c r="E5" s="14">
+        <v>89.81</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F15" si="0">ROUND(AVERAGE(H5:N5), 2)</f>
@@ -782,7 +785,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="1">
-        <v>88.44</v>
+        <v>88.91</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
@@ -827,7 +830,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="1">
-        <v>87.56</v>
+        <v>88.02</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
@@ -872,7 +875,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="1">
-        <v>86.68</v>
+        <v>87.14</v>
       </c>
       <c r="F8">
         <f>ROUND(AVERAGE(H8:M8), 2)</f>
@@ -917,7 +920,7 @@
         <v>26</v>
       </c>
       <c r="E9" s="1">
-        <v>85.82</v>
+        <v>86.27</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
@@ -952,22 +955,46 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="1">
+        <v>2700</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="E10" s="1">
-        <v>84.96</v>
-      </c>
-      <c r="F10" t="e">
+        <v>85.41</v>
+      </c>
+      <c r="F10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="N10" s="1"/>
+        <v>83.13</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14">
+        <v>83.6</v>
+      </c>
+      <c r="I10" s="1">
+        <v>83.1</v>
+      </c>
+      <c r="J10" s="1">
+        <v>82.75</v>
+      </c>
+      <c r="K10" s="14">
+        <v>82.4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>82.75</v>
+      </c>
+      <c r="M10" s="14">
+        <v>83.9</v>
+      </c>
+      <c r="N10" s="1">
+        <v>83.4</v>
+      </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11">
@@ -977,7 +1004,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1">
-        <v>84.11</v>
+        <v>84.56</v>
       </c>
       <c r="F11" t="e">
         <f t="shared" si="0"/>
@@ -998,7 +1025,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1">
-        <v>83.27</v>
+        <v>83.71</v>
       </c>
       <c r="F12" t="e">
         <f t="shared" si="0"/>
@@ -1019,7 +1046,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1">
-        <v>82.43</v>
+        <v>82.87</v>
       </c>
       <c r="F13" t="e">
         <f t="shared" si="0"/>
@@ -1040,7 +1067,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1">
-        <v>81.61</v>
+        <v>82.04</v>
       </c>
       <c r="F14" t="e">
         <f t="shared" si="0"/>
@@ -1061,7 +1088,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1">
-        <v>80.790000000000006</v>
+        <v>81.22</v>
       </c>
       <c r="F15" t="e">
         <f t="shared" si="0"/>
@@ -1074,18 +1101,98 @@
       <c r="L15" s="1"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="6" t="s">
+    <row r="16" spans="1:14">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="E16" s="14">
+        <v>80.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="E17" s="14">
+        <v>79.599999999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="E18" s="14">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="E19" s="14">
+        <v>78.010000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="E20" s="14">
+        <v>77.23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="E21" s="14">
+        <v>76.459999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="E22" s="14">
+        <v>75.69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="E23" s="14">
+        <v>74.930000000000007</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="E24" s="14">
+        <v>74.180000000000007</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="E25" s="14">
+        <v>73.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="14"/>
+      <c r="D31" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C31:D31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>Week</t>
   </si>
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +225,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1000,41 +1003,80 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="1">
+        <v>2700</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="E11" s="1">
         <v>84.56</v>
       </c>
-      <c r="F11" t="e">
+      <c r="F11">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="N11" s="1"/>
+        <v>83.74</v>
+      </c>
+      <c r="G11" s="2">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>83.9</v>
+      </c>
+      <c r="I11" s="15">
+        <v>83.9</v>
+      </c>
+      <c r="J11" s="15">
+        <v>83.9</v>
+      </c>
+      <c r="K11" s="15">
+        <v>83.6</v>
+      </c>
+      <c r="L11" s="15">
+        <v>83.1</v>
+      </c>
+      <c r="M11" s="15">
+        <v>83.9</v>
+      </c>
+      <c r="N11" s="15">
+        <v>83.9</v>
+      </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="1">
+        <v>2700</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>26</v>
+      </c>
       <c r="E12" s="1">
         <v>83.71</v>
       </c>
-      <c r="F12" t="e">
+      <c r="F12">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>83.05</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="H12" s="1">
+        <v>83.9</v>
+      </c>
+      <c r="I12" s="15">
+        <v>83.9</v>
+      </c>
+      <c r="J12" s="1">
+        <v>82.25</v>
+      </c>
+      <c r="K12" s="15">
+        <v>82.15</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="N12" s="1"/>
     </row>
@@ -1185,10 +1227,10 @@
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="15"/>
+      <c r="D31" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>Week</t>
   </si>
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +225,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1062,9 +1065,11 @@
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>83.05</v>
-      </c>
-      <c r="G12" s="2"/>
+        <v>82.66</v>
+      </c>
+      <c r="G12" s="2">
+        <v>4</v>
+      </c>
       <c r="H12" s="1">
         <v>83.9</v>
       </c>
@@ -1077,26 +1082,43 @@
       <c r="K12" s="15">
         <v>82.15</v>
       </c>
-      <c r="L12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="L12" s="16">
+        <v>82.15</v>
+      </c>
+      <c r="M12" s="16">
+        <v>82.15</v>
+      </c>
+      <c r="N12" s="16">
+        <v>82.15</v>
+      </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="16">
+        <v>2700</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="E13" s="1">
         <v>82.87</v>
       </c>
-      <c r="F13" t="e">
+      <c r="F13">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>81.55</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="H13" s="1">
+        <v>81.8</v>
+      </c>
+      <c r="I13" s="1">
+        <v>81.3</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="L13" s="1"/>
       <c r="N13" s="1"/>
@@ -1227,10 +1249,10 @@
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="16"/>
+      <c r="D31" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +225,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1110,7 +1113,7 @@
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>81.55</v>
+        <v>81.569999999999993</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="1">
@@ -1119,8 +1122,18 @@
       <c r="I13" s="1">
         <v>81.3</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="1">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="K13" s="17">
+        <v>81.75</v>
+      </c>
+      <c r="L13" s="17">
+        <v>81.75</v>
+      </c>
+      <c r="M13" s="17">
+        <v>81.400000000000006</v>
+      </c>
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14">
@@ -1249,10 +1262,10 @@
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="17"/>
+      <c r="D31" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Week</t>
   </si>
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +225,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1113,9 +1116,11 @@
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>81.569999999999993</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>81.59</v>
+      </c>
+      <c r="G13" s="2">
+        <v>3</v>
+      </c>
       <c r="H13" s="1">
         <v>81.8</v>
       </c>
@@ -1134,27 +1139,51 @@
       <c r="M13" s="17">
         <v>81.400000000000006</v>
       </c>
-      <c r="N13" s="1"/>
+      <c r="N13" s="1">
+        <v>81.7</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="18">
+        <v>2700</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="E14" s="1">
         <v>82.04</v>
       </c>
-      <c r="F14" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="F14">
+        <f>ROUND(AVERAGE(I14:N14), 2)</f>
+        <v>80.97</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
+      </c>
+      <c r="H14" s="18">
+        <v>81.7</v>
+      </c>
+      <c r="I14" s="18">
+        <v>81.7</v>
+      </c>
+      <c r="J14" s="1">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="K14" s="18">
+        <v>81.05</v>
+      </c>
+      <c r="L14" s="1">
+        <v>80.5</v>
+      </c>
+      <c r="M14" s="18">
+        <v>80.2</v>
+      </c>
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14">
@@ -1262,10 +1291,10 @@
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="18"/>
+      <c r="D31" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -195,7 +195,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +225,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1161,7 +1164,7 @@
       </c>
       <c r="F14">
         <f>ROUND(AVERAGE(I14:N14), 2)</f>
-        <v>80.97</v>
+        <v>80.84</v>
       </c>
       <c r="G14" s="2">
         <v>5</v>
@@ -1184,7 +1187,9 @@
       <c r="M14" s="18">
         <v>80.2</v>
       </c>
-      <c r="N14" s="1"/>
+      <c r="N14" s="19">
+        <v>80.2</v>
+      </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15">
@@ -1291,10 +1296,10 @@
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="19"/>
+      <c r="D31" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>Week</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>Some Walk</t>
+  </si>
+  <si>
+    <t>200g</t>
+  </si>
+  <si>
+    <t>4 * Walking</t>
   </si>
 </sst>
 </file>
@@ -195,7 +201,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -225,6 +231,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1195,22 +1207,46 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="20">
+        <v>2700</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>28</v>
+      </c>
       <c r="E15" s="1">
         <v>81.22</v>
       </c>
-      <c r="F15" t="e">
+      <c r="F15">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="N15" s="1"/>
+        <v>80.91</v>
+      </c>
+      <c r="G15" s="2">
+        <v>6</v>
+      </c>
+      <c r="H15" s="1">
+        <v>80.5</v>
+      </c>
+      <c r="I15" s="1">
+        <v>81.349999999999994</v>
+      </c>
+      <c r="J15" s="1">
+        <v>81.349999999999994</v>
+      </c>
+      <c r="K15" s="20">
+        <v>81</v>
+      </c>
+      <c r="L15" s="1">
+        <v>80.650000000000006</v>
+      </c>
+      <c r="M15" s="20">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="N15" s="1">
+        <v>80.900000000000006</v>
+      </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16">
@@ -1296,10 +1332,10 @@
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="20"/>
+      <c r="D31" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Week</t>
   </si>
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -231,6 +231,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -770,7 +773,7 @@
         <v>89.81</v>
       </c>
       <c r="F5">
-        <f t="shared" ref="F5:F15" si="0">ROUND(AVERAGE(H5:N5), 2)</f>
+        <f t="shared" ref="F5:F20" si="0">ROUND(AVERAGE(H5:N5), 2)</f>
         <v>87.7</v>
       </c>
       <c r="G5" s="2">
@@ -1123,7 +1126,7 @@
       <c r="C13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="22" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="1">
@@ -1168,7 +1171,7 @@
       <c r="C14" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="22" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="1">
@@ -1252,43 +1255,96 @@
       <c r="A16">
         <v>15</v>
       </c>
+      <c r="B16" s="22">
+        <v>2701</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>26</v>
+      </c>
       <c r="E16" s="14">
         <v>80.41</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>80.19</v>
+      </c>
+      <c r="G16" s="2">
+        <v>4</v>
+      </c>
+      <c r="H16" s="22">
+        <v>80.45</v>
+      </c>
+      <c r="I16" s="22">
+        <v>80.5</v>
+      </c>
+      <c r="J16" s="22">
+        <v>80.55</v>
+      </c>
+      <c r="K16" s="22">
+        <v>80.55</v>
+      </c>
+      <c r="L16" s="22">
+        <v>79.75</v>
+      </c>
+      <c r="M16" s="22">
+        <v>79.75</v>
+      </c>
+      <c r="N16" s="22">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="E17" s="14">
         <v>79.599999999999994</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="E18" s="14">
         <v>78.8</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="E19" s="14">
         <v>78.010000000000005</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="E20" s="14">
         <v>77.23</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1296,7 +1352,7 @@
         <v>76.459999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1304,7 +1360,7 @@
         <v>75.69</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1312,7 +1368,7 @@
         <v>74.930000000000007</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1320,7 +1376,7 @@
         <v>74.180000000000007</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1328,14 +1384,14 @@
         <v>73.44</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="22"/>
+      <c r="D31" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel/weight_loss_plan.xlsx
+++ b/excel/weight_loss_plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
   <si>
     <t>Week</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>4 * Walking</t>
+  </si>
+  <si>
+    <t>2500-2600</t>
   </si>
 </sst>
 </file>
@@ -201,7 +204,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -231,6 +234,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1256,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="22">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="C16" s="22" t="s">
         <v>27</v>
@@ -1296,31 +1302,82 @@
         <v>79.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>16</v>
       </c>
+      <c r="B17" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="E17" s="14">
         <v>79.599999999999994</v>
       </c>
-      <c r="F17" t="e">
+      <c r="F17">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>79.98</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="H17" s="23">
+        <v>79.75</v>
+      </c>
+      <c r="I17" s="23">
+        <v>79.5</v>
+      </c>
+      <c r="J17" s="23">
+        <v>80.95</v>
+      </c>
+      <c r="K17" s="23">
+        <v>80.25</v>
+      </c>
+      <c r="L17" s="23">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="M17" s="23">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="N17" s="23">
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>17</v>
       </c>
+      <c r="B18" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="E18" s="14">
         <v>78.8</v>
       </c>
-      <c r="F18" t="e">
+      <c r="F18">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>79.180000000000007</v>
+      </c>
+      <c r="H18" s="23">
+        <v>79.3</v>
+      </c>
+      <c r="I18" s="23">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="J18" s="23">
+        <v>79.349999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1332,7 +1389,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1344,7 +1401,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1352,7 +1409,7 @@
         <v>76.459999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1360,7 +1417,7 @@
         <v>75.69</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1368,7 +1425,7 @@
         <v>74.930000000000007</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1376,7 +1433,7 @@
         <v>74.180000000000007</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1384,14 +1441,14 @@
         <v>73.44</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:14">
       <c r="B31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="23"/>
+      <c r="D31" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
